--- a/tmp/prevention-export-work/extracted/EASM单次服务成果清单_外部风险_测试001[影子]_2026-07-03.xlsx
+++ b/tmp/prevention-export-work/extracted/EASM单次服务成果清单_外部风险_测试001[影子]_2026-07-03.xlsx
@@ -47,7 +47,7 @@
     <t>119</t>
   </si>
   <si>
-    <t>深信服-安服-权星 18291349681</t>
+    <t>深信服-安服-欧彪 17685079275</t>
   </si>
   <si>
     <t>shier、深信服科技股份有限公司</t>
